--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/PENNSYLVANIA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/PENNSYLVANIA_2019.xlsx
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C178">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C476">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C491">
